--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/08,09,26 Останкино Сыры/дв 08,09,26 днрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/08,09,26 Останкино Сыры/дв 08,09,26 днрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\08,09,26 Останкино Сыры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAC6603-DBF5-47CD-AF99-D6E5A16DC943}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE268D0-0550-4759-AB84-D94041E066C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>4421577 Спред растительно-сливочный "Сливочный вкус" 82,5% 180гр  Останкино</t>
-  </si>
-  <si>
-    <t>03,09,26 - нет на заводе / 27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
   </si>
   <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
@@ -340,6 +337,9 @@
   <si>
     <t>итого1</t>
   </si>
+  <si>
+    <t>10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
+  </si>
 </sst>
 </file>
 
@@ -386,7 +386,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,6 +412,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,7 +457,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -468,6 +474,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2604,25 +2611,25 @@
         <v>16</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>17</v>
@@ -2709,22 +2716,22 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="U4" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="V4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="W4" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="X4" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -2761,7 +2768,7 @@
       <c r="AK4" s="1"/>
       <c r="AL4" s="1"/>
       <c r="AM4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
@@ -2834,7 +2841,7 @@
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>3933</v>
+        <v>3885</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" ref="U5" si="1">SUM(U6:U499)</f>
@@ -2999,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AL6" s="1">
         <f>G6*R6</f>
@@ -3116,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AL7" s="1">
         <f t="shared" ref="AL7:AL47" si="8">G7*R7</f>
@@ -3427,9 +3434,8 @@
         <v>24</v>
       </c>
       <c r="S10" s="5"/>
-      <c r="T10" s="5">
-        <f>VLOOKUP(A10,заказ!A:B,2,0)</f>
-        <v>24</v>
+      <c r="T10" s="16">
+        <v>0</v>
       </c>
       <c r="U10" s="5"/>
       <c r="V10" s="13"/>
@@ -3474,7 +3480,7 @@
         <v>1.8</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AL10" s="1">
         <f t="shared" si="8"/>
@@ -3502,7 +3508,7 @@
     </row>
     <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>35</v>
@@ -3541,9 +3547,8 @@
         <v>24</v>
       </c>
       <c r="S11" s="5"/>
-      <c r="T11" s="5">
-        <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
-        <v>24</v>
+      <c r="T11" s="16">
+        <v>0</v>
       </c>
       <c r="U11" s="5"/>
       <c r="V11" s="13"/>
@@ -3588,7 +3593,7 @@
         <v>2</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AL11" s="1">
         <f t="shared" si="8"/>
@@ -3616,7 +3621,7 @@
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>40</v>
@@ -3729,7 +3734,7 @@
     </row>
     <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>35</v>
@@ -3816,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AL13" s="1">
         <f t="shared" si="8"/>
@@ -3844,7 +3849,7 @@
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>35</v>
@@ -3967,7 +3972,7 @@
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -4061,7 +4066,7 @@
         <v>8.4</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" si="8"/>
@@ -4089,7 +4094,7 @@
     </row>
     <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -4212,7 +4217,7 @@
     </row>
     <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>35</v>
@@ -4311,7 +4316,7 @@
         <v>15.8</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AL17" s="1">
         <f t="shared" si="8"/>
@@ -4339,7 +4344,7 @@
     </row>
     <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>35</v>
@@ -4460,7 +4465,7 @@
     </row>
     <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>35</v>
@@ -4583,7 +4588,7 @@
     </row>
     <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>35</v>
@@ -4706,7 +4711,7 @@
     </row>
     <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -4829,7 +4834,7 @@
     </row>
     <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -4916,7 +4921,7 @@
         <v>0.8</v>
       </c>
       <c r="AK22" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AL22" s="1">
         <f t="shared" si="8"/>
@@ -4944,7 +4949,7 @@
     </row>
     <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -5057,7 +5062,7 @@
     </row>
     <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>35</v>
@@ -5180,7 +5185,7 @@
     </row>
     <row r="25" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
@@ -5303,7 +5308,7 @@
     </row>
     <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -5424,7 +5429,7 @@
     </row>
     <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
@@ -5547,7 +5552,7 @@
     </row>
     <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
@@ -5642,7 +5647,7 @@
         <v>14.6</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AL28" s="1">
         <f t="shared" si="8"/>
@@ -5670,7 +5675,7 @@
     </row>
     <row r="29" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -5767,7 +5772,7 @@
         <v>51.2</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AL29" s="1">
         <f t="shared" si="8"/>
@@ -5795,7 +5800,7 @@
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>35</v>
@@ -5884,7 +5889,7 @@
         <v>6.2</v>
       </c>
       <c r="AK30" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AL30" s="1">
         <f t="shared" si="8"/>
@@ -5912,7 +5917,7 @@
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>35</v>
@@ -6006,7 +6011,7 @@
         <v>3.6</v>
       </c>
       <c r="AK31" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL31" s="1">
         <f t="shared" si="8"/>
@@ -6034,7 +6039,7 @@
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>35</v>
@@ -6157,7 +6162,7 @@
     </row>
     <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>35</v>
@@ -6253,7 +6258,7 @@
         <v>9</v>
       </c>
       <c r="AK33" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AL33" s="1">
         <f t="shared" si="8"/>
@@ -6281,7 +6286,7 @@
     </row>
     <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
@@ -6402,7 +6407,7 @@
     </row>
     <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
@@ -6525,7 +6530,7 @@
     </row>
     <row r="36" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>40</v>
@@ -6612,7 +6617,7 @@
         <v>0.67120000000000002</v>
       </c>
       <c r="AK36" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AL36" s="1">
         <f t="shared" si="8"/>
@@ -6640,7 +6645,7 @@
     </row>
     <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>40</v>
@@ -6733,7 +6738,7 @@
         <v>3.8391999999999999</v>
       </c>
       <c r="AK37" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL37" s="1">
         <f t="shared" si="8"/>
@@ -6761,7 +6766,7 @@
     </row>
     <row r="38" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>40</v>
@@ -6882,7 +6887,7 @@
     </row>
     <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>40</v>
@@ -6969,7 +6974,7 @@
         <v>4.4596</v>
       </c>
       <c r="AK39" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AL39" s="1">
         <f t="shared" si="8"/>
@@ -6997,7 +7002,7 @@
     </row>
     <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>35</v>
@@ -7120,7 +7125,7 @@
     </row>
     <row r="41" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -7237,7 +7242,7 @@
     </row>
     <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>40</v>
@@ -7328,7 +7333,7 @@
         <v>1.3344</v>
       </c>
       <c r="AK42" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AL42" s="1">
         <f t="shared" si="8"/>
@@ -7356,7 +7361,7 @@
     </row>
     <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>35</v>
@@ -7477,7 +7482,7 @@
     </row>
     <row r="44" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>35</v>
@@ -7596,7 +7601,7 @@
     </row>
     <row r="45" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>40</v>
@@ -7683,7 +7688,7 @@
         <v>5.3572000000000006</v>
       </c>
       <c r="AK45" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AL45" s="1">
         <f t="shared" si="8"/>
@@ -7711,7 +7716,7 @@
     </row>
     <row r="46" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>35</v>
@@ -7830,7 +7835,7 @@
     </row>
     <row r="47" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>40</v>
@@ -7919,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AL47" s="1">
         <f t="shared" si="8"/>
@@ -33286,7 +33291,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>24</v>
@@ -33294,7 +33299,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4">
         <v>120</v>
@@ -33302,7 +33307,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>192</v>
@@ -33310,7 +33315,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>240</v>
@@ -33318,7 +33323,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7">
         <v>180</v>
@@ -33326,7 +33331,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>48</v>
@@ -33334,7 +33339,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -33342,7 +33347,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>230</v>
@@ -33350,7 +33355,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>130</v>
@@ -33358,7 +33363,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -33366,7 +33371,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13">
         <v>184</v>
@@ -33374,7 +33379,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14">
         <v>216</v>
@@ -33382,7 +33387,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15">
         <v>120</v>
@@ -33390,7 +33395,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16">
         <v>130</v>
@@ -33398,7 +33403,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17">
         <v>560</v>
@@ -33406,7 +33411,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>20</v>
@@ -33414,7 +33419,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19">
         <v>430</v>
@@ -33422,7 +33427,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20">
         <v>80</v>
@@ -33430,7 +33435,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21">
         <v>80</v>
@@ -33438,7 +33443,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22">
         <v>16</v>
@@ -33446,7 +33451,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B23">
         <v>50</v>
@@ -33454,7 +33459,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24">
         <v>432</v>
@@ -33462,7 +33467,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25">
         <v>12</v>
@@ -33470,7 +33475,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26">
         <v>160</v>
@@ -33478,7 +33483,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27">
         <v>60</v>
@@ -33486,7 +33491,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B28">
         <v>20</v>
@@ -33504,7 +33509,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1">
         <v>160</v>
